--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-procedurede-transport-patient.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-procedurede-transport-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5327" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5327" uniqueCount="658">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette entrée de type act permet de décrire le transport d'un patient/usager lors d'un déplacement (entrée ou sortie d'hôpital, ...).</t>
+    <t>FrProcedureTransportPatient permet de décrire le transport d'un patient/usager lors d'un déplacement (entrée ou sortie d'hôpital, ...).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -459,10 +459,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Autres Precision</t>
-  </si>
-  <si>
-    <t>Autres précision sur le trajet ou le transport du patient.</t>
+    <t>Extension - Fr Autres Precision</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer les autres précision sur le trajet ou le transport du patient.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -805,7 +805,10 @@
 </t>
   </si>
   <si>
-    <t>Qualifier du code</t>
+    <t>Extension - Qualifier du code</t>
+  </si>
+  <si>
+    <t>Extension permettant d’associer à un code une précision (qualifier).</t>
   </si>
   <si>
     <t>Procedure.code.coding.extension:qualifier1.id</t>
@@ -1748,7 +1751,7 @@
 </t>
   </si>
   <si>
-    <t>Fr Lieu de départ du transport</t>
+    <t>Extension - Fr Lieu de départ du transport</t>
   </si>
   <si>
     <t>Extension pour représenter le lieu de départ d’un transport (patient ou professionnel).</t>
@@ -5303,7 +5306,7 @@
         <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>134</v>
+        <v>253</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5383,10 +5386,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5495,10 +5498,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5607,13 +5610,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="B29" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="C29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>77</v>
@@ -5721,10 +5724,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5833,10 +5836,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5945,10 +5948,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5974,13 +5977,13 @@
         <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5988,7 +5991,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>77</v>
@@ -6030,7 +6033,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>87</v>
@@ -6059,10 +6062,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6088,10 +6091,10 @@
         <v>200</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6103,7 +6106,7 @@
         <v>77</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>77</v>
@@ -6142,7 +6145,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6171,13 +6174,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>77</v>
@@ -6202,7 +6205,7 @@
         <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
         <v>134</v>
@@ -6285,10 +6288,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6397,10 +6400,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6509,10 +6512,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6538,13 +6541,13 @@
         <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6552,7 +6555,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>77</v>
@@ -6594,7 +6597,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>87</v>
@@ -6623,10 +6626,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6652,10 +6655,10 @@
         <v>200</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6706,7 +6709,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6735,10 +6738,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6764,13 +6767,13 @@
         <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6778,7 +6781,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>77</v>
@@ -6820,7 +6823,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>87</v>
@@ -6849,10 +6852,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6875,13 +6878,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6932,7 +6935,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6961,13 +6964,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>248</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>77</v>
@@ -6995,7 +6998,7 @@
         <v>252</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>134</v>
+        <v>253</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7075,10 +7078,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7187,10 +7190,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7198,7 +7201,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>79</v>
@@ -7299,13 +7302,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>77</v>
@@ -7413,10 +7416,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7525,10 +7528,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7637,10 +7640,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7666,13 +7669,13 @@
         <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7680,7 +7683,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>77</v>
@@ -7722,7 +7725,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>87</v>
@@ -7751,10 +7754,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7780,10 +7783,10 @@
         <v>200</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7795,7 +7798,7 @@
         <v>77</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>77</v>
@@ -7834,7 +7837,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7863,13 +7866,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -7977,10 +7980,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8089,10 +8092,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8201,10 +8204,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8230,13 +8233,13 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8244,7 +8247,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>77</v>
@@ -8286,7 +8289,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>87</v>
@@ -8315,10 +8318,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8344,10 +8347,10 @@
         <v>200</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8398,7 +8401,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8427,10 +8430,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8539,10 +8542,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8653,10 +8656,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8769,10 +8772,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8881,10 +8884,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8995,10 +8998,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9024,16 +9027,16 @@
         <v>101</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9062,7 +9065,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -9080,7 +9083,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9098,21 +9101,21 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9138,13 +9141,13 @@
         <v>228</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9194,7 +9197,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9212,21 +9215,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9252,14 +9255,14 @@
         <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9308,7 +9311,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9326,21 +9329,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9366,14 +9369,14 @@
         <v>228</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9422,7 +9425,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9440,21 +9443,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9477,19 +9480,19 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9538,7 +9541,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9556,21 +9559,21 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9596,16 +9599,16 @@
         <v>228</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9654,7 +9657,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9672,21 +9675,21 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9712,13 +9715,13 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9726,7 +9729,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>77</v>
@@ -9768,7 +9771,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>87</v>
@@ -9797,10 +9800,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9823,13 +9826,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9880,7 +9883,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9909,10 +9912,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9938,16 +9941,16 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9996,7 +9999,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10014,21 +10017,21 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10054,13 +10057,13 @@
         <v>228</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10110,7 +10113,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10128,21 +10131,21 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10168,14 +10171,14 @@
         <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -10224,7 +10227,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10242,21 +10245,21 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10282,14 +10285,14 @@
         <v>228</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10338,7 +10341,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10356,21 +10359,21 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10393,19 +10396,19 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10454,7 +10457,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10472,21 +10475,21 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10512,16 +10515,16 @@
         <v>228</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10570,7 +10573,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10588,25 +10591,25 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10625,13 +10628,13 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10682,7 +10685,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>87</v>
@@ -10697,24 +10700,24 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10737,16 +10740,16 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10796,7 +10799,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10811,24 +10814,24 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10851,16 +10854,16 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10898,17 +10901,17 @@
         <v>77</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10923,27 +10926,27 @@
         <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>77</v>
@@ -10965,16 +10968,16 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11024,7 +11027,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11039,24 +11042,24 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11079,13 +11082,13 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11136,7 +11139,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11154,10 +11157,10 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>77</v>
@@ -11165,10 +11168,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11191,13 +11194,13 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11248,7 +11251,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11266,10 +11269,10 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -11277,10 +11280,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11303,13 +11306,13 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11360,7 +11363,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11375,10 +11378,10 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11389,10 +11392,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11501,10 +11504,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11615,14 +11618,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11644,10 +11647,10 @@
         <v>132</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>149</v>
@@ -11702,7 +11705,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11731,10 +11734,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11760,14 +11763,14 @@
         <v>200</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -11795,10 +11798,10 @@
         <v>204</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>77</v>
@@ -11816,7 +11819,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11831,24 +11834,24 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11871,17 +11874,17 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11930,7 +11933,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>87</v>
@@ -11945,24 +11948,24 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12071,10 +12074,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12183,13 +12186,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="B87" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="C87" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>77</v>
@@ -12211,13 +12214,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12297,10 +12300,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12409,10 +12412,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12420,7 +12423,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>79</v>
@@ -12521,13 +12524,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="B90" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="C90" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>77</v>
@@ -12635,10 +12638,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12747,10 +12750,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12859,10 +12862,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12888,13 +12891,13 @@
         <v>101</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12902,7 +12905,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>77</v>
@@ -12944,7 +12947,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>87</v>
@@ -12973,10 +12976,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13002,10 +13005,10 @@
         <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13014,7 +13017,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>77</v>
@@ -13036,7 +13039,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -13054,7 +13057,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13083,13 +13086,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>77</v>
@@ -13197,10 +13200,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13309,10 +13312,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13421,10 +13424,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13450,13 +13453,13 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13464,7 +13467,7 @@
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>77</v>
@@ -13506,7 +13509,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -13535,10 +13538,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13564,10 +13567,10 @@
         <v>200</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13618,7 +13621,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13647,10 +13650,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13759,10 +13762,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13873,10 +13876,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13989,10 +13992,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14101,10 +14104,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14215,10 +14218,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14244,16 +14247,16 @@
         <v>101</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14302,7 +14305,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14320,21 +14323,21 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14360,13 +14363,13 @@
         <v>228</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14416,7 +14419,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14434,21 +14437,21 @@
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14474,14 +14477,14 @@
         <v>107</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -14491,7 +14494,7 @@
         <v>77</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>77</v>
@@ -14530,7 +14533,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14548,21 +14551,21 @@
         <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14588,14 +14591,14 @@
         <v>228</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -14644,7 +14647,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14662,21 +14665,21 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14699,19 +14702,19 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -14760,7 +14763,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14778,21 +14781,21 @@
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14818,16 +14821,16 @@
         <v>228</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14876,7 +14879,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14894,24 +14897,24 @@
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>77</v>
@@ -15019,10 +15022,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15131,10 +15134,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15243,10 +15246,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15272,13 +15275,13 @@
         <v>101</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15286,7 +15289,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>77</v>
@@ -15328,7 +15331,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>87</v>
@@ -15357,10 +15360,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15383,13 +15386,13 @@
         <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15440,7 +15443,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15469,10 +15472,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15498,13 +15501,13 @@
         <v>101</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15512,7 +15515,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>77</v>
@@ -15554,7 +15557,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>87</v>
@@ -15583,10 +15586,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15609,13 +15612,13 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15666,7 +15669,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15695,10 +15698,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15724,13 +15727,13 @@
         <v>228</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15780,7 +15783,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15789,7 +15792,7 @@
         <v>87</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>99</v>
@@ -15809,10 +15812,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15838,13 +15841,13 @@
         <v>101</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15870,13 +15873,13 @@
         <v>77</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>77</v>
@@ -15894,7 +15897,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15923,10 +15926,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15952,13 +15955,13 @@
         <v>153</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16008,7 +16011,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16026,7 +16029,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -16037,10 +16040,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16066,13 +16069,13 @@
         <v>228</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16122,7 +16125,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16151,10 +16154,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16177,17 +16180,17 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>77</v>
@@ -16236,7 +16239,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16254,7 +16257,7 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -16265,10 +16268,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16291,17 +16294,17 @@
         <v>88</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -16350,7 +16353,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16368,10 +16371,10 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>77</v>
@@ -16379,10 +16382,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16491,10 +16494,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16605,13 +16608,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="B126" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="C126" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>77</v>
@@ -16633,13 +16636,13 @@
         <v>77</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16719,13 +16722,13 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>77</v>
@@ -16747,13 +16750,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16833,10 +16836,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16862,13 +16865,13 @@
         <v>228</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16918,7 +16921,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16927,7 +16930,7 @@
         <v>87</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>99</v>
@@ -16947,10 +16950,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16976,13 +16979,13 @@
         <v>101</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17008,13 +17011,13 @@
         <v>77</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>77</v>
@@ -17032,7 +17035,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17061,10 +17064,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17090,13 +17093,13 @@
         <v>153</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17146,7 +17149,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17164,7 +17167,7 @@
         <v>77</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>77</v>
@@ -17175,10 +17178,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17204,13 +17207,13 @@
         <v>228</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17260,7 +17263,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17289,10 +17292,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17318,13 +17321,13 @@
         <v>200</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17353,10 +17356,10 @@
         <v>204</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>77</v>
@@ -17374,7 +17377,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17389,13 +17392,13 @@
         <v>99</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>77</v>
@@ -17403,10 +17406,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17429,16 +17432,16 @@
         <v>88</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17488,7 +17491,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17503,13 +17506,13 @@
         <v>99</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>77</v>
@@ -17517,10 +17520,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17546,13 +17549,13 @@
         <v>200</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17581,10 +17584,10 @@
         <v>204</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>77</v>
@@ -17602,7 +17605,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17620,21 +17623,21 @@
         <v>77</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17660,13 +17663,13 @@
         <v>200</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17695,10 +17698,10 @@
         <v>204</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -17716,7 +17719,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17734,7 +17737,7 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
@@ -17745,10 +17748,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17771,16 +17774,16 @@
         <v>77</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17830,7 +17833,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17848,7 +17851,7 @@
         <v>77</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>77</v>
@@ -17859,10 +17862,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17888,13 +17891,13 @@
         <v>200</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -17923,10 +17926,10 @@
         <v>204</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>77</v>
@@ -17944,7 +17947,7 @@
         <v>77</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -17962,7 +17965,7 @@
         <v>77</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>77</v>
@@ -17973,10 +17976,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17999,17 +18002,17 @@
         <v>77</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -18058,7 +18061,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -18076,7 +18079,7 @@
         <v>77</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>77</v>
@@ -18087,10 +18090,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18116,10 +18119,10 @@
         <v>200</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18149,10 +18152,10 @@
         <v>204</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>77</v>
@@ -18170,7 +18173,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18188,7 +18191,7 @@
         <v>77</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>77</v>
@@ -18199,10 +18202,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18225,13 +18228,13 @@
         <v>77</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18282,7 +18285,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18297,24 +18300,24 @@
         <v>99</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18337,13 +18340,13 @@
         <v>77</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18394,7 +18397,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18412,7 +18415,7 @@
         <v>77</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>77</v>
@@ -18423,10 +18426,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18535,10 +18538,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18649,14 +18652,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -18678,10 +18681,10 @@
         <v>132</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>149</v>
@@ -18736,7 +18739,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18765,10 +18768,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18794,10 +18797,10 @@
         <v>200</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18827,10 +18830,10 @@
         <v>111</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>77</v>
@@ -18848,7 +18851,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -18866,7 +18869,7 @@
         <v>77</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>77</v>
@@ -18877,10 +18880,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18903,13 +18906,13 @@
         <v>77</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -18960,7 +18963,7 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>87</v>
@@ -18978,7 +18981,7 @@
         <v>77</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>77</v>
@@ -18989,10 +18992,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19015,19 +19018,19 @@
         <v>77</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>77</v>
@@ -19076,7 +19079,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19094,7 +19097,7 @@
         <v>77</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>77</v>
@@ -19105,10 +19108,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19134,13 +19137,13 @@
         <v>200</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19169,10 +19172,10 @@
         <v>204</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>77</v>
@@ -19190,7 +19193,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19208,7 +19211,7 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>77</v>
